--- a/Hand_edited_log/1/student/cuongnvhe181200/TC3/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/cuongnvhe181200/TC3/GradeDetail.xlsx
@@ -1077,10 +1077,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>55752</x:v>
+        <x:v>51716</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1133,10 +1133,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>55752</x:v>
+        <x:v>51716</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,10 +1189,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>55752</x:v>
+        <x:v>51716</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1245,10 +1245,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>55752</x:v>
+        <x:v>51716</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>46</x:v>
@@ -1301,10 +1301,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>55752</x:v>
+        <x:v>51716</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>56</x:v>
@@ -1413,10 +1413,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>55752</x:v>
+        <x:v>51716</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1469,10 +1469,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>55752</x:v>
+        <x:v>51716</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,10 +1525,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>55752</x:v>
+        <x:v>51716</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R10" s="5" t="s">
         <x:v>62</x:v>
@@ -1581,10 +1581,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>55752</x:v>
+        <x:v>51716</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>
